--- a/test_gl_data.xlsx
+++ b/test_gl_data.xlsx
@@ -412,7 +412,7 @@
         <v>3004</v>
       </c>
       <c r="B2">
-        <v>4664.4</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="3">
@@ -420,7 +420,7 @@
         <v>3032</v>
       </c>
       <c r="B3">
-        <v>11614</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="4">
@@ -428,7 +428,7 @@
         <v>3055</v>
       </c>
       <c r="B4">
-        <v>2250</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="5">
@@ -436,7 +436,7 @@
         <v>3071</v>
       </c>
       <c r="B5">
-        <v>850</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
